--- a/notebooks/xml_content.xlsx
+++ b/notebooks/xml_content.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A119"/>
+  <dimension ref="A1:A101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,14 +466,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">            &lt;MsgId&gt;1PSS-26894&lt;/MsgId&gt;</t>
+          <t xml:space="preserve">            &lt;MsgId&gt;1PSS-26952&lt;/MsgId&gt;</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">            &lt;CreDtTm&gt;2026-07-29T10:04:03&lt;/CreDtTm&gt;</t>
+          <t xml:space="preserve">            &lt;CreDtTm&gt;2026-09-02T14:31:57&lt;/CreDtTm&gt;</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            &lt;PmtInfId&gt;06021B02506-1010&lt;/PmtInfId&gt;</t>
+          <t xml:space="preserve">            &lt;PmtInfId&gt;06021B02506-1011&lt;/PmtInfId&gt;</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">            &lt;ReqdExctnDt&gt;2026-08-28&lt;/ReqdExctnDt&gt;</t>
+          <t xml:space="preserve">            &lt;ReqdExctnDt&gt;2026-07-31&lt;/ReqdExctnDt&gt;</t>
         </is>
       </c>
     </row>
@@ -816,14 +816,14 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    &lt;InstrId&gt;06021B02506-1010&lt;/InstrId&gt;</t>
+          <t xml:space="preserve">                    &lt;InstrId&gt;06021B02506-1011&lt;/InstrId&gt;</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    &lt;EndToEndId&gt;06021B02506-1010&lt;/EndToEndId&gt;</t>
+          <t xml:space="preserve">                    &lt;EndToEndId&gt;06021B02506-1011&lt;/EndToEndId&gt;</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    &lt;InstdAmt Ccy="USD"&gt;33302&lt;/InstdAmt&gt;</t>
+          <t xml:space="preserve">                    &lt;InstdAmt Ccy="USD"&gt;200000&lt;/InstdAmt&gt;</t>
         </is>
       </c>
     </row>
@@ -879,383 +879,257 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        &lt;BIC&gt;PUNBINBBISB&lt;/BIC&gt;</t>
+          <t xml:space="preserve">                        &lt;BIC&gt;SGABLULL&lt;/BIC&gt;</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        &lt;ClrSysMmbId&gt;</t>
+          <t xml:space="preserve">                        &lt;Nm&gt;SOCIETE GENERALE  LUXEMBOURG S.A.&lt;/Nm&gt;</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">                            &lt;MmbId&gt;11111111&lt;/MmbId&gt;</t>
+          <t xml:space="preserve">                        &lt;PstlAdr&gt;</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        &lt;/ClrSysMmbId&gt;</t>
+          <t xml:space="preserve">                            &lt;TwnNm&gt;11 Avenue Emile Reuter, L-2420 Luxe&lt;/TwnNm&gt;</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        &lt;Nm&gt;PUNJAB NATIONAL BANK&lt;/Nm&gt;</t>
+          <t xml:space="preserve">                            &lt;Ctry&gt;LU&lt;/Ctry&gt;</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        &lt;PstlAdr&gt;</t>
+          <t xml:space="preserve">                        &lt;/PstlAdr&gt;</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">                            &lt;PstCd&gt;600002&lt;/PstCd&gt;</t>
+          <t xml:space="preserve">                    &lt;/FinInstnId&gt;</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">                            &lt;TwnNm&gt;Chennai&lt;/TwnNm&gt;</t>
+          <t xml:space="preserve">                &lt;/CdtrAgt&gt;</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">                            &lt;Ctry&gt;IN&lt;/Ctry&gt;</t>
+          <t xml:space="preserve">                &lt;Cdtr&gt;</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        &lt;/PstlAdr&gt;</t>
+          <t xml:space="preserve">                    &lt;Nm&gt;ABBOTT INVESTMENTS LUXEMBOURG SARL&lt;/Nm&gt;</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    &lt;/FinInstnId&gt;</t>
+          <t xml:space="preserve">                    &lt;PstlAdr&gt;</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">                &lt;/CdtrAgt&gt;</t>
+          <t xml:space="preserve">                        &lt;StrtNm&gt;26 Boulevard Royal, L-2449 Luxembourg, Luxembourg&lt;/StrtNm&gt;</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">                &lt;Cdtr&gt;</t>
+          <t xml:space="preserve">                        &lt;PstCd&gt;L-2449&lt;/PstCd&gt;</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    &lt;Nm&gt;TENTH PLANET TECHNOLOGIES P LTD&lt;/Nm&gt;</t>
+          <t xml:space="preserve">                        &lt;TwnNm&gt;Luxembourg&lt;/TwnNm&gt;</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    &lt;PstlAdr&gt;</t>
+          <t xml:space="preserve">                        &lt;Ctry&gt;LU&lt;/Ctry&gt;</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        &lt;PstCd&gt;600002&lt;/PstCd&gt;</t>
+          <t xml:space="preserve">                    &lt;/PstlAdr&gt;</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        &lt;StrtNm&gt;807AnnaSalaiFL6thP.T.Lee Build,Chennai600002,India&lt;/StrtNm&gt;</t>
+          <t xml:space="preserve">                &lt;/Cdtr&gt;</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        &lt;TwnNm&gt;Chennai&lt;/TwnNm&gt;</t>
+          <t xml:space="preserve">                &lt;CdtrAcct&gt;</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        &lt;Ctry&gt;IN&lt;/Ctry&gt;</t>
+          <t xml:space="preserve">                    &lt;Id&gt;</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    &lt;/PstlAdr&gt;</t>
+          <t xml:space="preserve">                        &lt;IBAN&gt;LU590612332812600USD&lt;/IBAN&gt;</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">                &lt;/Cdtr&gt;</t>
+          <t xml:space="preserve">                    &lt;/Id&gt;</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">                &lt;CdtrAcct&gt;</t>
+          <t xml:space="preserve">                &lt;/CdtrAcct&gt;</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    &lt;Id&gt;</t>
+          <t xml:space="preserve">                &lt;RltdRmtInf&gt;</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        &lt;Othr&gt;</t>
+          <t xml:space="preserve">                    &lt;RmtLctnMtd&gt;EMAL&lt;/RmtLctnMtd&gt;</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">                            &lt;Id&gt;12134011000089&lt;/Id&gt;</t>
+          <t xml:space="preserve">                    &lt;RmtLctnElctrncAdr&gt;VN-3A-STP@abbott.com&lt;/RmtLctnElctrncAdr&gt;</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        &lt;/Othr&gt;</t>
+          <t xml:space="preserve">                &lt;/RltdRmtInf&gt;</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    &lt;/Id&gt;</t>
+          <t xml:space="preserve">                &lt;RltdRmtInf&gt;</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">                &lt;/CdtrAcct&gt;</t>
+          <t xml:space="preserve">                    &lt;RmtLctnMtd&gt;EMAL&lt;/RmtLctnMtd&gt;</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">                &lt;RltdRmtInf&gt;</t>
+          <t xml:space="preserve">                    &lt;RmtLctnElctrncAdr&gt;victoria.luo@abbott.com&lt;/RmtLctnElctrncAdr&gt;</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    &lt;RmtLctnMtd&gt;EMAL&lt;/RmtLctnMtd&gt;</t>
+          <t xml:space="preserve">                &lt;/RltdRmtInf&gt;</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    &lt;RmtLctnElctrncAdr&gt;VN-3A-STP@abbott.com&lt;/RmtLctnElctrncAdr&gt;</t>
+          <t xml:space="preserve">                &lt;RmtInf&gt;</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">                &lt;/RltdRmtInf&gt;</t>
+          <t xml:space="preserve">                    &lt;Ustrd&gt;TT Hoa Don 72026&lt;/Ustrd&gt;</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">                &lt;RltdRmtInf&gt;</t>
+          <t xml:space="preserve">                &lt;/RmtInf&gt;</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    &lt;RmtLctnMtd&gt;EMAL&lt;/RmtLctnMtd&gt;</t>
+          <t xml:space="preserve">            &lt;/CdtTrfTxInf&gt;</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">                    &lt;RmtLctnElctrncAdr&gt;kumaran@tenthplanet.in&lt;/RmtLctnElctrncAdr&gt;</t>
+          <t xml:space="preserve">        &lt;/PmtInf&gt;</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">                &lt;/RltdRmtInf&gt;</t>
+          <t xml:space="preserve">    &lt;/CstmrCdtTrfInitn&gt;</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                &lt;RmtInf&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                    &lt;Ustrd&gt;TT Hoa Don 7890 &lt;/Ustrd&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                    &lt;Strd&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        &lt;RfrdDocInf&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                            &lt;RltdDt&gt;2026-07-15&lt;/RltdDt&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        &lt;/RfrdDocInf&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        &lt;RfrdDocAmt&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                            &lt;DuePyblAmt Ccy="USD"&gt;33302&lt;/DuePyblAmt&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        &lt;/RfrdDocAmt&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        &lt;CdtrRefInf&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                            &lt;Ref&gt; &lt;/Ref&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        &lt;/CdtrRefInf&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        &lt;AddtlRmtInf&gt;Hoa don 7890&lt;/AddtlRmtInf&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                    &lt;/Strd&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                &lt;/RmtInf&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            &lt;/CdtTrfTxInf&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        &lt;/PmtInf&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    &lt;/CstmrCdtTrfInitn&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
         <is>
           <t>&lt;/Document&gt;</t>
         </is>
